--- a/examples/extensions/thai_bim/examples/stair-U-BBS.xlsx
+++ b/examples/extensions/thai_bim/examples/stair-U-BBS.xlsx
@@ -228,7 +228,7 @@
       </c>
       <c r="N2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="O2" s="0" t="inlineStr">
@@ -334,7 +334,7 @@
       </c>
       <c r="N3" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="O3" s="0" t="inlineStr">
@@ -440,7 +440,7 @@
       </c>
       <c r="N4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="O4" s="0" t="inlineStr">
@@ -546,7 +546,7 @@
       </c>
       <c r="N5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="O5" s="0" t="inlineStr">
@@ -652,7 +652,7 @@
       </c>
       <c r="N6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="O6" s="0" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="N7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="O7" s="0" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="N8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="O8" s="0" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="N9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="O9" s="0" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="N10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="O10" s="0" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="N11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="O11" s="0" t="inlineStr">
@@ -1328,12 +1328,12 @@
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">eca0027c7b214bec</t>
+          <t xml:space="preserve">08635ebca9ef40ae</t>
         </is>
       </c>
       <c r="B2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C2" s="0" t="inlineStr">
@@ -1401,12 +1401,12 @@
     <row r="3">
       <c r="A3" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">f3b50c3f03394db5</t>
+          <t xml:space="preserve">1dd9ee5ba0a34afe</t>
         </is>
       </c>
       <c r="B3" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C3" s="0" t="inlineStr">
@@ -1474,12 +1474,12 @@
     <row r="4">
       <c r="A4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">21a219ff8d4145ed</t>
+          <t xml:space="preserve">032994e226434a80</t>
         </is>
       </c>
       <c r="B4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C4" s="0" t="inlineStr">
@@ -1547,12 +1547,12 @@
     <row r="5">
       <c r="A5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">17119a02bf604c16</t>
+          <t xml:space="preserve">4fbed6f790e14b57</t>
         </is>
       </c>
       <c r="B5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C5" s="0" t="inlineStr">
@@ -1620,12 +1620,12 @@
     <row r="6">
       <c r="A6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5f4f02c0b28b4385</t>
+          <t xml:space="preserve">66e5e15c0c9846e9</t>
         </is>
       </c>
       <c r="B6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C6" s="0" t="inlineStr">
@@ -1693,12 +1693,12 @@
     <row r="7">
       <c r="A7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ca438a8f5ff34444</t>
+          <t xml:space="preserve">608134f92d434626</t>
         </is>
       </c>
       <c r="B7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C7" s="0" t="inlineStr">
@@ -1766,12 +1766,12 @@
     <row r="8">
       <c r="A8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">04d0b1fef93f4d04</t>
+          <t xml:space="preserve">cba0708742194eb1</t>
         </is>
       </c>
       <c r="B8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C8" s="0" t="inlineStr">
@@ -1839,12 +1839,12 @@
     <row r="9">
       <c r="A9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">af24f35f9cac407f</t>
+          <t xml:space="preserve">3ead6ed4ee614a84</t>
         </is>
       </c>
       <c r="B9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C9" s="0" t="inlineStr">
@@ -1912,12 +1912,12 @@
     <row r="10">
       <c r="A10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">a3355c024a2940bf</t>
+          <t xml:space="preserve">e3cdb9f07ee34aac</t>
         </is>
       </c>
       <c r="B10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C10" s="0" t="inlineStr">
@@ -1985,12 +1985,12 @@
     <row r="11">
       <c r="A11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9175c9d5f6044897</t>
+          <t xml:space="preserve">e5cb1e59787a4f45</t>
         </is>
       </c>
       <c r="B11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C11" s="0" t="inlineStr">
@@ -2058,12 +2058,12 @@
     <row r="12">
       <c r="A12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">b7b0bc5322934fc9</t>
+          <t xml:space="preserve">86b6b2ececfa4e97</t>
         </is>
       </c>
       <c r="B12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C12" s="0" t="inlineStr">
@@ -2131,12 +2131,12 @@
     <row r="13">
       <c r="A13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">7b150955eb044d9a</t>
+          <t xml:space="preserve">212384a2344d4808</t>
         </is>
       </c>
       <c r="B13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C13" s="0" t="inlineStr">
@@ -2204,12 +2204,12 @@
     <row r="14">
       <c r="A14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">7481e1b9d01b4e79</t>
+          <t xml:space="preserve">83ef9dbfa5184a15</t>
         </is>
       </c>
       <c r="B14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C14" s="0" t="inlineStr">
@@ -2277,12 +2277,12 @@
     <row r="15">
       <c r="A15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">26ef7e0ee79e400c</t>
+          <t xml:space="preserve">9c22f01413ef40bb</t>
         </is>
       </c>
       <c r="B15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C15" s="0" t="inlineStr">
@@ -2350,12 +2350,12 @@
     <row r="16">
       <c r="A16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">d00f5f45c12a4ecb</t>
+          <t xml:space="preserve">6a1c101f59fa4b20</t>
         </is>
       </c>
       <c r="B16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C16" s="0" t="inlineStr">
@@ -2423,12 +2423,12 @@
     <row r="17">
       <c r="A17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">6715bd5e6b84489e</t>
+          <t xml:space="preserve">e31845e400234b7d</t>
         </is>
       </c>
       <c r="B17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C17" s="0" t="inlineStr">
@@ -2496,12 +2496,12 @@
     <row r="18">
       <c r="A18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">a1508fc0ab4c4d7c</t>
+          <t xml:space="preserve">a58f90de4d7d4ba5</t>
         </is>
       </c>
       <c r="B18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C18" s="0" t="inlineStr">
@@ -2569,12 +2569,12 @@
     <row r="19">
       <c r="A19" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">e9e12c0bbc3f455e</t>
+          <t xml:space="preserve">b02d8ea1f65b42e2</t>
         </is>
       </c>
       <c r="B19" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C19" s="0" t="inlineStr">
@@ -2642,12 +2642,12 @@
     <row r="20">
       <c r="A20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5e18d7416f2e49a9</t>
+          <t xml:space="preserve">c5ec5a6d49624722</t>
         </is>
       </c>
       <c r="B20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C20" s="0" t="inlineStr">
@@ -2715,12 +2715,12 @@
     <row r="21">
       <c r="A21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">6b88cc7f58294ef8</t>
+          <t xml:space="preserve">3f20dc6692484e5d</t>
         </is>
       </c>
       <c r="B21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C21" s="0" t="inlineStr">
@@ -2788,12 +2788,12 @@
     <row r="22">
       <c r="A22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1f0f0abad9e24e42</t>
+          <t xml:space="preserve">d9a7c5e35a67441e</t>
         </is>
       </c>
       <c r="B22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C22" s="0" t="inlineStr">
@@ -2861,12 +2861,12 @@
     <row r="23">
       <c r="A23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">6e9b33bb9b7e4cac</t>
+          <t xml:space="preserve">efd73f9ccf92474c</t>
         </is>
       </c>
       <c r="B23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C23" s="0" t="inlineStr">
@@ -2934,12 +2934,12 @@
     <row r="24">
       <c r="A24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">06dac3f85b924e33</t>
+          <t xml:space="preserve">3a2fd8f082ec454d</t>
         </is>
       </c>
       <c r="B24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C24" s="0" t="inlineStr">
@@ -3007,12 +3007,12 @@
     <row r="25">
       <c r="A25" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">591376848e2a4a3a</t>
+          <t xml:space="preserve">c77a6d5ac7e347d8</t>
         </is>
       </c>
       <c r="B25" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C25" s="0" t="inlineStr">
@@ -3080,12 +3080,12 @@
     <row r="26">
       <c r="A26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">05e0522cf67347b5</t>
+          <t xml:space="preserve">3fae4b4f11454ddf</t>
         </is>
       </c>
       <c r="B26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C26" s="0" t="inlineStr">
@@ -3153,12 +3153,12 @@
     <row r="27">
       <c r="A27" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">908942e9b2644f48</t>
+          <t xml:space="preserve">794d15a48fb34ce2</t>
         </is>
       </c>
       <c r="B27" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C27" s="0" t="inlineStr">
@@ -3226,12 +3226,12 @@
     <row r="28">
       <c r="A28" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">363a148690d84df6</t>
+          <t xml:space="preserve">c303c78e30ae4893</t>
         </is>
       </c>
       <c r="B28" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C28" s="0" t="inlineStr">
@@ -3299,12 +3299,12 @@
     <row r="29">
       <c r="A29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">843a7fa24cc14bd9</t>
+          <t xml:space="preserve">39bd4f36d7a94e67</t>
         </is>
       </c>
       <c r="B29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C29" s="0" t="inlineStr">
@@ -3372,12 +3372,12 @@
     <row r="30">
       <c r="A30" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">0f4a43f818134fc9</t>
+          <t xml:space="preserve">7bb4b5afa34b40ec</t>
         </is>
       </c>
       <c r="B30" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C30" s="0" t="inlineStr">
@@ -3445,12 +3445,12 @@
     <row r="31">
       <c r="A31" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">6d8bb52ac3754a30</t>
+          <t xml:space="preserve">e32c8e7ec9f44fda</t>
         </is>
       </c>
       <c r="B31" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C31" s="0" t="inlineStr">
@@ -3518,12 +3518,12 @@
     <row r="32">
       <c r="A32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">68c445178e0d4819</t>
+          <t xml:space="preserve">346d57b1cbec4c54</t>
         </is>
       </c>
       <c r="B32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C32" s="0" t="inlineStr">
@@ -3591,12 +3591,12 @@
     <row r="33">
       <c r="A33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">80a3b76586e94708</t>
+          <t xml:space="preserve">97428474247149a0</t>
         </is>
       </c>
       <c r="B33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C33" s="0" t="inlineStr">
@@ -3664,12 +3664,12 @@
     <row r="34">
       <c r="A34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">b01835145ae24f45</t>
+          <t xml:space="preserve">2a634e062202400f</t>
         </is>
       </c>
       <c r="B34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C34" s="0" t="inlineStr">
@@ -3737,12 +3737,12 @@
     <row r="35">
       <c r="A35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">4377e94f1f4f402e</t>
+          <t xml:space="preserve">f940a0c271104069</t>
         </is>
       </c>
       <c r="B35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C35" s="0" t="inlineStr">
@@ -3810,12 +3810,12 @@
     <row r="36">
       <c r="A36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">eec8df644d474f86</t>
+          <t xml:space="preserve">3bdbc5a1dd2441ba</t>
         </is>
       </c>
       <c r="B36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C36" s="0" t="inlineStr">
@@ -3883,12 +3883,12 @@
     <row r="37">
       <c r="A37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">b77695fdbe7c4b5a</t>
+          <t xml:space="preserve">6ecc2a20d81d49aa</t>
         </is>
       </c>
       <c r="B37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C37" s="0" t="inlineStr">
@@ -3956,12 +3956,12 @@
     <row r="38">
       <c r="A38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">481fd635a05a46c7</t>
+          <t xml:space="preserve">2d73dc105b0b49a6</t>
         </is>
       </c>
       <c r="B38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C38" s="0" t="inlineStr">
@@ -4029,12 +4029,12 @@
     <row r="39">
       <c r="A39" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5e94dc5cad984252</t>
+          <t xml:space="preserve">31a989e351464222</t>
         </is>
       </c>
       <c r="B39" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C39" s="0" t="inlineStr">
@@ -4102,12 +4102,12 @@
     <row r="40">
       <c r="A40" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">a56d80a88fb14011</t>
+          <t xml:space="preserve">801eb12f497140f1</t>
         </is>
       </c>
       <c r="B40" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C40" s="0" t="inlineStr">
@@ -4175,12 +4175,12 @@
     <row r="41">
       <c r="A41" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9da8110d5e744fe0</t>
+          <t xml:space="preserve">15d544b36f96457d</t>
         </is>
       </c>
       <c r="B41" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C41" s="0" t="inlineStr">
@@ -4248,12 +4248,12 @@
     <row r="42">
       <c r="A42" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">6594fd65ad144936</t>
+          <t xml:space="preserve">5f3588cdea0a49a8</t>
         </is>
       </c>
       <c r="B42" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C42" s="0" t="inlineStr">
@@ -4321,12 +4321,12 @@
     <row r="43">
       <c r="A43" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">da5ed284743b4e15</t>
+          <t xml:space="preserve">e5d197487a294468</t>
         </is>
       </c>
       <c r="B43" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C43" s="0" t="inlineStr">
@@ -4394,12 +4394,12 @@
     <row r="44">
       <c r="A44" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">a8e0f1fc70fd4b8a</t>
+          <t xml:space="preserve">046e94188a6048ea</t>
         </is>
       </c>
       <c r="B44" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C44" s="0" t="inlineStr">
@@ -4467,12 +4467,12 @@
     <row r="45">
       <c r="A45" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">44fc1172da1042e8</t>
+          <t xml:space="preserve">7530d323df7f4a3f</t>
         </is>
       </c>
       <c r="B45" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C45" s="0" t="inlineStr">
@@ -4540,12 +4540,12 @@
     <row r="46">
       <c r="A46" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">7caa42dd913148ac</t>
+          <t xml:space="preserve">e9ffef3bcfe14d90</t>
         </is>
       </c>
       <c r="B46" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C46" s="0" t="inlineStr">
@@ -4613,12 +4613,12 @@
     <row r="47">
       <c r="A47" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">a8fe7c2e103b4f2b</t>
+          <t xml:space="preserve">1ce39524b3364bf3</t>
         </is>
       </c>
       <c r="B47" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C47" s="0" t="inlineStr">
@@ -4686,12 +4686,12 @@
     <row r="48">
       <c r="A48" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2050576d98b54d0e</t>
+          <t xml:space="preserve">c60af731fefd4d65</t>
         </is>
       </c>
       <c r="B48" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C48" s="0" t="inlineStr">
@@ -4759,12 +4759,12 @@
     <row r="49">
       <c r="A49" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">996f3fd02eba47e7</t>
+          <t xml:space="preserve">e0ddca872dcf4fd5</t>
         </is>
       </c>
       <c r="B49" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C49" s="0" t="inlineStr">
@@ -4832,12 +4832,12 @@
     <row r="50">
       <c r="A50" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">fe50cafb9c8e4901</t>
+          <t xml:space="preserve">4a0a206e84c24b2b</t>
         </is>
       </c>
       <c r="B50" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C50" s="0" t="inlineStr">
@@ -4905,12 +4905,12 @@
     <row r="51">
       <c r="A51" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">66fe1f2458594844</t>
+          <t xml:space="preserve">0c3e8e7a5ce84678</t>
         </is>
       </c>
       <c r="B51" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C51" s="0" t="inlineStr">
@@ -4978,12 +4978,12 @@
     <row r="52">
       <c r="A52" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">44acf10de8a34a2f</t>
+          <t xml:space="preserve">b4ac10d568dd41ee</t>
         </is>
       </c>
       <c r="B52" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C52" s="0" t="inlineStr">
@@ -5051,12 +5051,12 @@
     <row r="53">
       <c r="A53" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">808b9fe1a37947f2</t>
+          <t xml:space="preserve">989c7f36cf6b4896</t>
         </is>
       </c>
       <c r="B53" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C53" s="0" t="inlineStr">
@@ -5124,12 +5124,12 @@
     <row r="54">
       <c r="A54" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">41a3af3a43604644</t>
+          <t xml:space="preserve">a5174acc18c044fc</t>
         </is>
       </c>
       <c r="B54" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C54" s="0" t="inlineStr">
@@ -5197,12 +5197,12 @@
     <row r="55">
       <c r="A55" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">3622ad7071d54767</t>
+          <t xml:space="preserve">29703adbf30a4935</t>
         </is>
       </c>
       <c r="B55" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C55" s="0" t="inlineStr">
@@ -5270,12 +5270,12 @@
     <row r="56">
       <c r="A56" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1e9992db02a3449d</t>
+          <t xml:space="preserve">29dce9a9adc44f55</t>
         </is>
       </c>
       <c r="B56" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C56" s="0" t="inlineStr">
@@ -5343,12 +5343,12 @@
     <row r="57">
       <c r="A57" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">6b83919d969c45e6</t>
+          <t xml:space="preserve">8e7b8502b5ce4137</t>
         </is>
       </c>
       <c r="B57" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C57" s="0" t="inlineStr">
@@ -5416,12 +5416,12 @@
     <row r="58">
       <c r="A58" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">6333b78700ce4eeb</t>
+          <t xml:space="preserve">4b552ef1bfa0448d</t>
         </is>
       </c>
       <c r="B58" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C58" s="0" t="inlineStr">
@@ -5489,12 +5489,12 @@
     <row r="59">
       <c r="A59" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9d4c1dbef96245ef</t>
+          <t xml:space="preserve">b150174e750c418f</t>
         </is>
       </c>
       <c r="B59" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C59" s="0" t="inlineStr">
@@ -5562,12 +5562,12 @@
     <row r="60">
       <c r="A60" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">c48d8c11c76b44e2</t>
+          <t xml:space="preserve">723f823885ae4737</t>
         </is>
       </c>
       <c r="B60" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C60" s="0" t="inlineStr">
@@ -5635,12 +5635,12 @@
     <row r="61">
       <c r="A61" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">7cb3e97fb1bf4c3b</t>
+          <t xml:space="preserve">4fe8a87736e04340</t>
         </is>
       </c>
       <c r="B61" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C61" s="0" t="inlineStr">
@@ -5708,12 +5708,12 @@
     <row r="62">
       <c r="A62" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5bea49a4e5b9455c</t>
+          <t xml:space="preserve">d6907103aeb341f9</t>
         </is>
       </c>
       <c r="B62" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C62" s="0" t="inlineStr">
@@ -5781,12 +5781,12 @@
     <row r="63">
       <c r="A63" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">f7e2c0b9a5554cb2</t>
+          <t xml:space="preserve">3476ad9a4df5446c</t>
         </is>
       </c>
       <c r="B63" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C63" s="0" t="inlineStr">
@@ -5854,12 +5854,12 @@
     <row r="64">
       <c r="A64" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">62617ef846f040da</t>
+          <t xml:space="preserve">48775a3d43634752</t>
         </is>
       </c>
       <c r="B64" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C64" s="0" t="inlineStr">
@@ -5927,12 +5927,12 @@
     <row r="65">
       <c r="A65" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">d79123562b3e4819</t>
+          <t xml:space="preserve">cf87f89f3e274032</t>
         </is>
       </c>
       <c r="B65" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C65" s="0" t="inlineStr">
@@ -6000,12 +6000,12 @@
     <row r="66">
       <c r="A66" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bb9b1b01c01a49c0</t>
+          <t xml:space="preserve">a613161902b14321</t>
         </is>
       </c>
       <c r="B66" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C66" s="0" t="inlineStr">
@@ -6073,12 +6073,12 @@
     <row r="67">
       <c r="A67" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5695a299724049e2</t>
+          <t xml:space="preserve">538a3546572545e6</t>
         </is>
       </c>
       <c r="B67" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C67" s="0" t="inlineStr">
@@ -6146,12 +6146,12 @@
     <row r="68">
       <c r="A68" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">cb2f69942e394321</t>
+          <t xml:space="preserve">b7bd47bad9584774</t>
         </is>
       </c>
       <c r="B68" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C68" s="0" t="inlineStr">
@@ -6219,12 +6219,12 @@
     <row r="69">
       <c r="A69" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ae6db20eb53a49f6</t>
+          <t xml:space="preserve">1d19383834fe4c9a</t>
         </is>
       </c>
       <c r="B69" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C69" s="0" t="inlineStr">
@@ -6292,12 +6292,12 @@
     <row r="70">
       <c r="A70" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">299f4ff83fd24d9d</t>
+          <t xml:space="preserve">8af42919835744a6</t>
         </is>
       </c>
       <c r="B70" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C70" s="0" t="inlineStr">
@@ -6365,12 +6365,12 @@
     <row r="71">
       <c r="A71" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">da422c28235c4978</t>
+          <t xml:space="preserve">02f73cb73c6343e2</t>
         </is>
       </c>
       <c r="B71" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C71" s="0" t="inlineStr">
@@ -6438,12 +6438,12 @@
     <row r="72">
       <c r="A72" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5a053e43a6ac44e3</t>
+          <t xml:space="preserve">6ef474a6e1fa4fd5</t>
         </is>
       </c>
       <c r="B72" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C72" s="0" t="inlineStr">
@@ -6511,12 +6511,12 @@
     <row r="73">
       <c r="A73" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">6d8df5091d9b4d70</t>
+          <t xml:space="preserve">ea4f8ee4b2374291</t>
         </is>
       </c>
       <c r="B73" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C73" s="0" t="inlineStr">
@@ -6584,12 +6584,12 @@
     <row r="74">
       <c r="A74" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">41d75bf946b74e29</t>
+          <t xml:space="preserve">5ed7d10d9f2c48a0</t>
         </is>
       </c>
       <c r="B74" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C74" s="0" t="inlineStr">
@@ -6657,12 +6657,12 @@
     <row r="75">
       <c r="A75" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">4b0fb87990f943e9</t>
+          <t xml:space="preserve">0545756d88d94f71</t>
         </is>
       </c>
       <c r="B75" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C75" s="0" t="inlineStr">
@@ -6730,12 +6730,12 @@
     <row r="76">
       <c r="A76" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ab90b177d7794fd5</t>
+          <t xml:space="preserve">a0419e6c7f1d43d5</t>
         </is>
       </c>
       <c r="B76" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C76" s="0" t="inlineStr">
@@ -6803,12 +6803,12 @@
     <row r="77">
       <c r="A77" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">c5b2dbcd287f421f</t>
+          <t xml:space="preserve">b18f945e81094ba2</t>
         </is>
       </c>
       <c r="B77" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C77" s="0" t="inlineStr">
@@ -6876,12 +6876,12 @@
     <row r="78">
       <c r="A78" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">6c3e42cc41e1427e</t>
+          <t xml:space="preserve">2423e2262ad94d7e</t>
         </is>
       </c>
       <c r="B78" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C78" s="0" t="inlineStr">
@@ -6949,12 +6949,12 @@
     <row r="79">
       <c r="A79" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">069bda3a518a4fea</t>
+          <t xml:space="preserve">13a721631d7a4ab6</t>
         </is>
       </c>
       <c r="B79" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C79" s="0" t="inlineStr">
@@ -7022,12 +7022,12 @@
     <row r="80">
       <c r="A80" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1962420b3eae4c9d</t>
+          <t xml:space="preserve">3936a6dc62c14d6e</t>
         </is>
       </c>
       <c r="B80" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C80" s="0" t="inlineStr">
@@ -7095,12 +7095,12 @@
     <row r="81">
       <c r="A81" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">d8b9716258294573</t>
+          <t xml:space="preserve">6e9b2fca663b4628</t>
         </is>
       </c>
       <c r="B81" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C81" s="0" t="inlineStr">
@@ -7168,12 +7168,12 @@
     <row r="82">
       <c r="A82" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">0269a24023764d96</t>
+          <t xml:space="preserve">93d0bc24d91d4a38</t>
         </is>
       </c>
       <c r="B82" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C82" s="0" t="inlineStr">
@@ -7241,12 +7241,12 @@
     <row r="83">
       <c r="A83" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">7841b25d4d0d43ed</t>
+          <t xml:space="preserve">06dfe41802d24a07</t>
         </is>
       </c>
       <c r="B83" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C83" s="0" t="inlineStr">
@@ -7314,12 +7314,12 @@
     <row r="84">
       <c r="A84" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9955e14111b44abb</t>
+          <t xml:space="preserve">a0f32cf1400b4815</t>
         </is>
       </c>
       <c r="B84" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C84" s="0" t="inlineStr">
@@ -7387,12 +7387,12 @@
     <row r="85">
       <c r="A85" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">27f4915b5d5e4ea2</t>
+          <t xml:space="preserve">e306119adc2444b3</t>
         </is>
       </c>
       <c r="B85" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C85" s="0" t="inlineStr">
@@ -7460,12 +7460,12 @@
     <row r="86">
       <c r="A86" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">dad545b22a8345db</t>
+          <t xml:space="preserve">b99e7d0d4b80480a</t>
         </is>
       </c>
       <c r="B86" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C86" s="0" t="inlineStr">
@@ -7533,12 +7533,12 @@
     <row r="87">
       <c r="A87" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">57a570714cae4626</t>
+          <t xml:space="preserve">18383526fb164302</t>
         </is>
       </c>
       <c r="B87" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C87" s="0" t="inlineStr">
@@ -7606,12 +7606,12 @@
     <row r="88">
       <c r="A88" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ed8ea95ac9e94501</t>
+          <t xml:space="preserve">5ab9b59383df4ec9</t>
         </is>
       </c>
       <c r="B88" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C88" s="0" t="inlineStr">
@@ -7679,12 +7679,12 @@
     <row r="89">
       <c r="A89" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">0fbe1b8e25f149d7</t>
+          <t xml:space="preserve">43833e5fc9854d11</t>
         </is>
       </c>
       <c r="B89" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C89" s="0" t="inlineStr">
@@ -7752,12 +7752,12 @@
     <row r="90">
       <c r="A90" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">81024b86bded46f2</t>
+          <t xml:space="preserve">21cf967150c24683</t>
         </is>
       </c>
       <c r="B90" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C90" s="0" t="inlineStr">
@@ -7825,12 +7825,12 @@
     <row r="91">
       <c r="A91" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">4ca8c3905f3c49c1</t>
+          <t xml:space="preserve">a736bc47d0574dee</t>
         </is>
       </c>
       <c r="B91" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C91" s="0" t="inlineStr">
@@ -7898,12 +7898,12 @@
     <row r="92">
       <c r="A92" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">685621af132c47d6</t>
+          <t xml:space="preserve">2d7a32b0c53447bc</t>
         </is>
       </c>
       <c r="B92" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C92" s="0" t="inlineStr">
@@ -7971,12 +7971,12 @@
     <row r="93">
       <c r="A93" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">0f9b6876404642fd</t>
+          <t xml:space="preserve">93af5c5298c14a5e</t>
         </is>
       </c>
       <c r="B93" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C93" s="0" t="inlineStr">
@@ -8044,12 +8044,12 @@
     <row r="94">
       <c r="A94" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">40beb51762134227</t>
+          <t xml:space="preserve">c37fa60f30e649b5</t>
         </is>
       </c>
       <c r="B94" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C94" s="0" t="inlineStr">
@@ -8117,12 +8117,12 @@
     <row r="95">
       <c r="A95" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">547f2549aede4908</t>
+          <t xml:space="preserve">ec390a45dd634d65</t>
         </is>
       </c>
       <c r="B95" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C95" s="0" t="inlineStr">
@@ -8190,12 +8190,12 @@
     <row r="96">
       <c r="A96" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">152e93718c344668</t>
+          <t xml:space="preserve">d088ebcabea84215</t>
         </is>
       </c>
       <c r="B96" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C96" s="0" t="inlineStr">
@@ -8263,12 +8263,12 @@
     <row r="97">
       <c r="A97" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">d2a2db87c2a94df8</t>
+          <t xml:space="preserve">3f4ff5176fe44dcf</t>
         </is>
       </c>
       <c r="B97" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5064bbd3e3474211</t>
+          <t xml:space="preserve">77cf5355bc034018</t>
         </is>
       </c>
       <c r="C97" s="0" t="inlineStr">
